--- a/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
@@ -5596,7 +5596,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -40469,7 +40469,7 @@
           <t>A | 620呎 (3房)
 $1576万
 $25,421/呎
-(26年-08月-23日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -44281,7 +44281,7 @@
           <t>A | 482呎 (2房)
 $1225万
 $25,409/呎
-(26年-08月-26日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">

--- a/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
@@ -18047,38 +18047,30 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>14993000</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>24182</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K252" s="5" t="n">
+        <v>14993000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>24182</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -18087,7 +18079,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39855,7 +39847,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39865,7 +39857,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42030,12 +42022,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1499万
+$24,182/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">

--- a/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
@@ -38663,38 +38663,30 @@
       </c>
       <c r="F556" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H556" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I556" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H556" s="5" t="n">
+        <v>7929000</v>
+      </c>
+      <c r="I556" s="5" t="n">
+        <v>25827</v>
       </c>
       <c r="J556" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K556" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L556" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K556" s="5" t="n">
+        <v>7929000</v>
+      </c>
+      <c r="L556" s="5" t="n">
+        <v>25827</v>
       </c>
       <c r="M556" s="3" t="inlineStr">
         <is>
@@ -38703,7 +38695,7 @@
       </c>
       <c r="N556" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -44930,7 +44922,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44940,7 +44932,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45055,12 +45047,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 307呎 (1房)
-招标单位
--
-(在售)</t>
+$793万
+$25,827/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">

--- a/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay II/Miami Quay II_销控明细表.xlsx
@@ -22569,7 +22569,7 @@
         </is>
       </c>
       <c r="E317" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>7249000</v>
       </c>
       <c r="I317" s="5" t="n">
-        <v>22724</v>
+        <v>22796</v>
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>7249000</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>22724</v>
+        <v>22796</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>7231000</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>22668</v>
+        <v>22739</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>7231000</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>22668</v>
+        <v>22739</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>7213000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>22611</v>
+        <v>22682</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>7213000</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>22611</v>
+        <v>22682</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>7195000</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>22555</v>
+        <v>22626</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>7195000</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>22555</v>
+        <v>22626</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>7177000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>22498</v>
+        <v>22569</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>7177000</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>22498</v>
+        <v>22569</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>7159000</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>22442</v>
+        <v>22513</v>
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>7159000</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>22442</v>
+        <v>22513</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         </is>
       </c>
       <c r="E389" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>7142000</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>22389</v>
+        <v>22459</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>7142000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>22389</v>
+        <v>22459</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         </is>
       </c>
       <c r="E401" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>7106000</v>
       </c>
       <c r="I401" s="5" t="n">
-        <v>22276</v>
+        <v>22346</v>
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>7106000</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>22276</v>
+        <v>22346</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>7070000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>22163</v>
+        <v>22233</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>7070000</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>22163</v>
+        <v>22233</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         </is>
       </c>
       <c r="E437" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>7053000</v>
       </c>
       <c r="I437" s="5" t="n">
-        <v>22110</v>
+        <v>22179</v>
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>7053000</v>
       </c>
       <c r="L437" s="5" t="n">
-        <v>22110</v>
+        <v>22179</v>
       </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>7035000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>22053</v>
+        <v>22123</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>7035000</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>22053</v>
+        <v>22123</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>7018000</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>22000</v>
+        <v>22069</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>7018000</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>22000</v>
+        <v>22069</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>6989000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>20863</v>
+        <v>20925</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>6989000</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>20863</v>
+        <v>20925</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         </is>
       </c>
       <c r="E473" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>7000000</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>21944</v>
+        <v>22013</v>
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>7000000</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>21944</v>
+        <v>22013</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         </is>
       </c>
       <c r="E477" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>6971000</v>
       </c>
       <c r="I477" s="5" t="n">
-        <v>20809</v>
+        <v>20871</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>6971000</v>
       </c>
       <c r="L477" s="5" t="n">
-        <v>20809</v>
+        <v>20871</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>6982000</v>
       </c>
       <c r="I485" s="5" t="n">
-        <v>21887</v>
+        <v>21956</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>6982000</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>21887</v>
+        <v>21956</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         </is>
       </c>
       <c r="E489" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>6953000</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>20755</v>
+        <v>20817</v>
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>6953000</v>
       </c>
       <c r="L489" s="5" t="n">
-        <v>20755</v>
+        <v>20817</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         </is>
       </c>
       <c r="E495" s="4" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>5930000</v>
       </c>
       <c r="I495" s="5" t="n">
-        <v>23255</v>
+        <v>23164</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>5930000</v>
       </c>
       <c r="L495" s="5" t="n">
-        <v>23255</v>
+        <v>23164</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         </is>
       </c>
       <c r="E497" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F497" s="3" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>6948000</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>21781</v>
+        <v>21849</v>
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>6948000</v>
       </c>
       <c r="L497" s="5" t="n">
-        <v>21781</v>
+        <v>21849</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         </is>
       </c>
       <c r="E501" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>6919000</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>20654</v>
+        <v>20716</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>6919000</v>
       </c>
       <c r="L501" s="5" t="n">
-        <v>20654</v>
+        <v>20716</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>5915000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>23196</v>
+        <v>23105</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>5915000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>23196</v>
+        <v>23105</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         </is>
       </c>
       <c r="E507" s="4" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F507" s="3" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>6930000</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>21724</v>
+        <v>21792</v>
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>6930000</v>
       </c>
       <c r="L507" s="5" t="n">
-        <v>21724</v>
+        <v>21792</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         </is>
       </c>
       <c r="E511" s="4" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>6902000</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>20603</v>
+        <v>20665</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>6902000</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>20603</v>
+        <v>20665</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         </is>
       </c>
       <c r="E551" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F551" s="3" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>8460000</v>
       </c>
       <c r="I551" s="5" t="n">
-        <v>27468</v>
+        <v>27557</v>
       </c>
       <c r="J551" s="3" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>8460000</v>
       </c>
       <c r="L551" s="5" t="n">
-        <v>27468</v>
+        <v>27557</v>
       </c>
       <c r="M551" s="3" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         </is>
       </c>
       <c r="E555" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>8090000</v>
       </c>
       <c r="I555" s="5" t="n">
-        <v>26266</v>
+        <v>26352</v>
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>8090000</v>
       </c>
       <c r="L555" s="5" t="n">
-        <v>26266</v>
+        <v>26352</v>
       </c>
       <c r="M555" s="3" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         </is>
       </c>
       <c r="E560" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F560" s="3" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>7890000</v>
       </c>
       <c r="I560" s="5" t="n">
-        <v>25617</v>
+        <v>25700</v>
       </c>
       <c r="J560" s="3" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>7890000</v>
       </c>
       <c r="L560" s="5" t="n">
-        <v>25617</v>
+        <v>25700</v>
       </c>
       <c r="M560" s="3" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         </is>
       </c>
       <c r="E565" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>7850000</v>
       </c>
       <c r="I565" s="5" t="n">
-        <v>25487</v>
+        <v>25570</v>
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
@@ -39252,7 +39252,7 @@
         <v>7850000</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>25487</v>
+        <v>25570</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         </is>
       </c>
       <c r="E571" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>7811000</v>
       </c>
       <c r="I571" s="5" t="n">
-        <v>25360</v>
+        <v>25443</v>
       </c>
       <c r="J571" s="3" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>7811000</v>
       </c>
       <c r="L571" s="5" t="n">
-        <v>25360</v>
+        <v>25443</v>
       </c>
       <c r="M571" s="3" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         </is>
       </c>
       <c r="E572" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F572" s="3" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>7811000</v>
       </c>
       <c r="I572" s="5" t="n">
-        <v>25360</v>
+        <v>25443</v>
       </c>
       <c r="J572" s="3" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>7811000</v>
       </c>
       <c r="L572" s="5" t="n">
-        <v>25360</v>
+        <v>25443</v>
       </c>
       <c r="M572" s="3" t="inlineStr">
         <is>
@@ -42892,9 +42892,9 @@
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $725万
-$22,724/呎
+$22,796/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -42995,9 +42995,9 @@
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $723万
-$22,668/呎
+$22,739/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -43098,9 +43098,9 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $721万
-$22,611/呎
+$22,682/呎
 (26年-04月-27日)</t>
         </is>
       </c>
@@ -43201,9 +43201,9 @@
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $720万
-$22,555/呎
+$22,626/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -43304,9 +43304,9 @@
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $718万
-$22,498/呎
+$22,569/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -43407,9 +43407,9 @@
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $716万
-$22,442/呎
+$22,513/呎
 (26年-05月-13日)</t>
         </is>
       </c>
@@ -43510,9 +43510,9 @@
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $714万
-$22,389/呎
+$22,459/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -43613,9 +43613,9 @@
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $711万
-$22,276/呎
+$22,346/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -43819,9 +43819,9 @@
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $707万
-$22,163/呎
+$22,233/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -43922,9 +43922,9 @@
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $705万
-$22,110/呎
+$22,179/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -44025,9 +44025,9 @@
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $704万
-$22,053/呎
+$22,123/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -44096,9 +44096,9 @@
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>F | 335呎 (1房)
+          <t>F | 334呎 (1房)
 $699万
-$20,863/呎
+$20,925/呎
 (26年-03月-17日)</t>
         </is>
       </c>
@@ -44128,9 +44128,9 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $702万
-$22,000/呎
+$22,069/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -44199,9 +44199,9 @@
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>F | 335呎 (1房)
+          <t>F | 334呎 (1房)
 $697万
-$20,809/呎
+$20,871/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -44231,9 +44231,9 @@
       </c>
       <c r="K23" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $700万
-$21,944/呎
+$22,013/呎
 (26年-05月-20日)</t>
         </is>
       </c>
@@ -44302,9 +44302,9 @@
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>F | 335呎 (1房)
+          <t>F | 334呎 (1房)
 $695万
-$20,755/呎
+$20,817/呎
 (26年-05月-05日)</t>
         </is>
       </c>
@@ -44334,9 +44334,9 @@
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $698万
-$21,887/呎
+$21,956/呎
 (26年-05月-21日)</t>
         </is>
       </c>
@@ -44391,9 +44391,9 @@
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>F | 335呎 (1房)
+          <t>F | 334呎 (1房)
 $692万
-$20,654/呎
+$20,716/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -44423,9 +44423,9 @@
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $695万
-$21,781/呎
+$21,849/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -44439,9 +44439,9 @@
       </c>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>M | 255呎 (开放式)
+          <t>M | 256呎 (开放式)
 $593万
-$23,255/呎
+$23,164/呎
 (26年-05月-13日)</t>
         </is>
       </c>
@@ -44480,9 +44480,9 @@
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>F | 335呎 (1房)
+          <t>F | 334呎 (1房)
 $690万
-$20,603/呎
+$20,665/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -44512,9 +44512,9 @@
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>K | 319呎 (1房)
+          <t>K | 318呎 (1房)
 $693万
-$21,724/呎
+$21,792/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -44528,9 +44528,9 @@
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>M | 255呎 (开放式)
+          <t>M | 256呎 (开放式)
 $592万
-$23,196/呎
+$23,105/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -45002,9 +45002,9 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>C | 308呎 (1房)
+          <t>C | 307呎 (1房)
 $846万
-$27,468/呎
+$27,557/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -45057,9 +45057,9 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>D | 308呎 (1房)
+          <t>D | 307呎 (1房)
 $809万
-$26,266/呎
+$26,352/呎
 (26年-01月-26日)</t>
         </is>
       </c>
@@ -45104,9 +45104,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 308呎 (1房)
+          <t>D | 307呎 (1房)
 $789万
-$25,617/呎
+$25,700/呎
 (25年-12月-01日)</t>
         </is>
       </c>
@@ -45151,9 +45151,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 308呎 (1房)
+          <t>D | 307呎 (1房)
 $785万
-$25,487/呎
+$25,570/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -45182,17 +45182,17 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 308呎 (1房)
+          <t>B | 307呎 (1房)
 $781万
-$25,360/呎
+$25,443/呎
 (26年-05月-11日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>C | 308呎 (1房)
+          <t>C | 307呎 (1房)
 $781万
-$25,360/呎
+$25,443/呎
 (26年-05月-08日)</t>
         </is>
       </c>
